--- a/data-entry/csv_files/products.xlsx
+++ b/data-entry/csv_files/products.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+  <si>
+    <t>id</t>
+  </si>
   <si>
     <t>title</t>
   </si>
@@ -61,6 +64,9 @@
     <t>sales.discount</t>
   </si>
   <si>
+    <t>601d2f302bc1370f7a2d6288</t>
+  </si>
+  <si>
     <t>New Product</t>
   </si>
   <si>
@@ -79,10 +85,10 @@
     <t>Gigi</t>
   </si>
   <si>
-    <t>2024-01-02T09:40:55.693970562Z</t>
-  </si>
-  <si>
-    <t>2024-01-03T09:40:55.693978892Z</t>
+    <t>2024-01-02T10:21:51.843048931Z</t>
+  </si>
+  <si>
+    <t>2024-01-03T10:21:51.843051659Z</t>
   </si>
 </sst>
 </file>
@@ -151,24 +157,25 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Frame0" displayName="Frame0" ref="A1:O2" totalsRowShown="0">
-  <autoFilter ref="A1:O2"/>
-  <tableColumns count="15">
-    <tableColumn id="1" name="title" dataDxfId="0"/>
-    <tableColumn id="2" name="status" dataDxfId="0"/>
-    <tableColumn id="3" name="instockStatus" dataDxfId="0"/>
-    <tableColumn id="4" name="priceUnit" dataDxfId="0"/>
-    <tableColumn id="5" name="warranty" dataDxfId="1"/>
-    <tableColumn id="6" name="quantity" dataDxfId="1"/>
-    <tableColumn id="7" name="price" dataDxfId="2"/>
-    <tableColumn id="8" name="marketPrice" dataDxfId="2"/>
-    <tableColumn id="9" name="dealerPrice" dataDxfId="1"/>
-    <tableColumn id="10" name="discount" dataDxfId="1"/>
-    <tableColumn id="11" name="brandName" dataDxfId="0"/>
-    <tableColumn id="12" name="sales.name" dataDxfId="0"/>
-    <tableColumn id="13" name="sales.startDate" dataDxfId="0"/>
-    <tableColumn id="14" name="sales.endDate" dataDxfId="0"/>
-    <tableColumn id="15" name="sales.discount" dataDxfId="2"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Frame0" displayName="Frame0" ref="A1:P2" totalsRowShown="0">
+  <autoFilter ref="A1:P2"/>
+  <tableColumns count="16">
+    <tableColumn id="1" name="id" dataDxfId="0"/>
+    <tableColumn id="2" name="title" dataDxfId="0"/>
+    <tableColumn id="3" name="status" dataDxfId="0"/>
+    <tableColumn id="4" name="instockStatus" dataDxfId="0"/>
+    <tableColumn id="5" name="priceUnit" dataDxfId="0"/>
+    <tableColumn id="6" name="warranty" dataDxfId="1"/>
+    <tableColumn id="7" name="quantity" dataDxfId="1"/>
+    <tableColumn id="8" name="price" dataDxfId="2"/>
+    <tableColumn id="9" name="marketPrice" dataDxfId="2"/>
+    <tableColumn id="10" name="dealerPrice" dataDxfId="1"/>
+    <tableColumn id="11" name="discount" dataDxfId="1"/>
+    <tableColumn id="12" name="brandName" dataDxfId="0"/>
+    <tableColumn id="13" name="sales.name" dataDxfId="0"/>
+    <tableColumn id="14" name="sales.startDate" dataDxfId="0"/>
+    <tableColumn id="15" name="sales.endDate" dataDxfId="0"/>
+    <tableColumn id="16" name="sales.discount" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -459,10 +466,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:16">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -508,51 +515,57 @@
       <c r="O1" t="s">
         <v>14</v>
       </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:16">
       <c r="A2" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" s="2">
+        <v>19</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" s="2">
         <v>0</v>
       </c>
-      <c r="F2" s="2">
+      <c r="G2" s="2">
         <v>1</v>
-      </c>
-      <c r="G2" s="3">
-        <v>0</v>
       </c>
       <c r="H2" s="3">
         <v>0</v>
       </c>
-      <c r="I2" s="2">
+      <c r="I2" s="3">
         <v>0</v>
       </c>
       <c r="J2" s="2">
         <v>0</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>19</v>
+      <c r="K2" s="2">
+        <v>0</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="O2" s="3">
+        <v>23</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="P2" s="3">
         <v>24.5</v>
       </c>
     </row>
